--- a/tests/Verificacoes.xlsx
+++ b/tests/Verificacoes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\My Drive\UNI\2025\2025-2Sem\LDS - Lab Dev Soft\Dev\main\stock-manager\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8390CF49-EAF5-4F75-9A5A-91EB1B6AF19E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2AF1028-7F00-4DD4-B416-9198DFDE8C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="689" activeTab="6" xr2:uid="{255F9818-EC5A-46FF-9D2F-15463B870A74}"/>
   </bookViews>
@@ -20,6 +20,7 @@
     <sheet name="CheckT3_20260427" sheetId="16" r:id="rId5"/>
     <sheet name="CheckT4_20260430" sheetId="8" r:id="rId6"/>
     <sheet name="Plano de Testes" sheetId="9" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="17" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">CheckT3_20260419!$A$1:$K$36</definedName>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1846" uniqueCount="718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1985" uniqueCount="732">
   <si>
     <t>Foi possível verificar bem a versão final, mas não reconstruir todo o percurso intermédio entre versões com detalhe total.</t>
   </si>
@@ -1061,9 +1062,6 @@
     <t>Auto/Manual</t>
   </si>
   <si>
-    <t>Remoção com stock insuficiente</t>
-  </si>
-  <si>
     <t>Testes de Integração – Explosão</t>
   </si>
   <si>
@@ -1097,12 +1095,6 @@
     <t>Proteção do estado interno (deep copy)</t>
   </si>
   <si>
-    <t>Estado interno mantém-se inalterado</t>
-  </si>
-  <si>
-    <t>Quantidade superior ao stock</t>
-  </si>
-  <si>
     <t>Testes Unitários Dinâmicos – Caixa Aberta</t>
   </si>
   <si>
@@ -1145,15 +1137,6 @@
     <t>Equipa: Codezilla</t>
   </si>
   <si>
-    <t>Estado consistente</t>
-  </si>
-  <si>
-    <t>Várias ações seguidas</t>
-  </si>
-  <si>
-    <t>Sequência de operações</t>
-  </si>
-  <si>
     <t>Stock insuficiente</t>
   </si>
   <si>
@@ -1535,9 +1518,6 @@
     <t>MS4</t>
   </si>
   <si>
-    <t>MU5</t>
-  </si>
-  <si>
     <t>MU6</t>
   </si>
   <si>
@@ -1592,9 +1572,6 @@
     <t>CI4</t>
   </si>
   <si>
-    <t>CI7</t>
-  </si>
-  <si>
     <t>KA</t>
   </si>
   <si>
@@ -1898,6 +1875,9 @@
     <t>O código actual mantém input na View, coordenação no Controller, lógica e persistência no Model, apresentação na View, e suporta o plano de integração definido</t>
   </si>
   <si>
+    <t>Criado/Testado por:</t>
+  </si>
+  <si>
     <t>Confirmado: o Model não referencia directamente a View nem o Controller.</t>
   </si>
   <si>
@@ -2202,6 +2182,69 @@
   </si>
   <si>
     <t>Avaliar remoção de ref das assinaturas e chamadas, mantendo a mesma lógica de preenchimento da lista</t>
+  </si>
+  <si>
+    <t>7;11;44;46</t>
+  </si>
+  <si>
+    <t>7;44;53</t>
+  </si>
+  <si>
+    <t>7;44</t>
+  </si>
+  <si>
+    <t>26;27;44</t>
+  </si>
+  <si>
+    <t>25;48</t>
+  </si>
+  <si>
+    <t>46;48</t>
+  </si>
+  <si>
+    <t>24;48</t>
+  </si>
+  <si>
+    <t>26;51;55</t>
+  </si>
+  <si>
+    <t>25;46</t>
+  </si>
+  <si>
+    <t>19;20</t>
+  </si>
+  <si>
+    <t>Confirmado: quando o Model sinaliza stock insuficiente, a View apresenta "✖ Stock insuficiente." e a aplicação continua a correr.</t>
+  </si>
+  <si>
+    <t>Confirmado: com lista vazia, a View apresenta "--- STOCK ---" e "Sem produtos." sem erro.</t>
+  </si>
+  <si>
+    <t>Confirmado: MostrarStock apenas percorre a lista recebida e apresenta os produtos, sem alterar os dados.</t>
+  </si>
+  <si>
+    <t>Confirmado: após CarregarDados(), o fluxo Controller -&gt; View apresenta os produtos no formato "Nome - Quantidade Unidade (mín: QuantidadeMinima)".</t>
+  </si>
+  <si>
+    <t>Confirmado: os fluxos de consulta, adição, remoção, reposição e saída têm apresentação coerente na View e não mostram erros de navegação.</t>
+  </si>
+  <si>
+    <t>Confirmado: com stock suficiente, o Model decrementa a quantidade, guarda os dados e a View apresenta confirmação de remoção.</t>
+  </si>
+  <si>
+    <t>Confirmado: com stock insuficiente, o Model não altera os dados, sinaliza erro e a aplicação continua sem crash.</t>
+  </si>
+  <si>
+    <t>Confirmado: os produtos com Quantidade &lt; QuantidadeMinima são filtrados pelo Model e apresentados correctamente pela View.</t>
+  </si>
+  <si>
+    <t>Confirmado: após registo e remoção, GuardarDados() persiste o estado; num reinício, CarregarDados() repõe esse estado.</t>
+  </si>
+  <si>
+    <t>Confirmado: quando a remoção falha, o Model termina sem alterar a quantidade e a consulta posterior devolve o estado anterior.</t>
+  </si>
+  <si>
+    <t>Confirmado: opções inválidas repetidas apenas geram mensagem de erro, mantendo o ciclo principal estável e sem recursão nem crash.</t>
   </si>
 </sst>
 </file>
@@ -6176,13 +6219,13 @@
         <v>51</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>39</v>
@@ -6342,7 +6385,7 @@
         <v>33</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>34</v>
@@ -6374,7 +6417,7 @@
         <v>33</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>34</v>
@@ -6406,7 +6449,7 @@
         <v>33</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>34</v>
@@ -6438,7 +6481,7 @@
         <v>33</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>34</v>
@@ -6814,7 +6857,7 @@
         <v>33</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="J30" s="6" t="s">
         <v>34</v>
@@ -6849,10 +6892,10 @@
         <v>222</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="J31" s="6" t="s">
         <v>49</v>
@@ -6887,10 +6930,10 @@
         <v>223</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="J32" s="6" t="s">
         <v>49</v>
@@ -6954,7 +6997,7 @@
         <v>33</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="J34" s="6" t="s">
         <v>34</v>
@@ -6986,13 +7029,13 @@
         <v>58</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="J35" s="6" t="s">
         <v>49</v>
@@ -7012,19 +7055,19 @@
         <v>54</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>33</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="J36" s="6" t="s">
         <v>34</v>
@@ -7041,19 +7084,19 @@
         <v>54</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="F37" s="6" t="s">
         <v>33</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="J37" s="6" t="s">
         <v>34</v>
@@ -7070,19 +7113,19 @@
         <v>54</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>33</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="J38" s="6" t="s">
         <v>34</v>
@@ -7099,19 +7142,19 @@
         <v>54</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="F39" s="6" t="s">
         <v>33</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="J39" s="6" t="s">
         <v>34</v>
@@ -7128,19 +7171,19 @@
         <v>54</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>33</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="J40" s="6" t="s">
         <v>34</v>
@@ -7157,19 +7200,19 @@
         <v>54</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="F41" s="6" t="s">
         <v>33</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="J41" s="6" t="s">
         <v>34</v>
@@ -7186,19 +7229,19 @@
         <v>54</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>33</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="J42" s="6" t="s">
         <v>34</v>
@@ -7215,25 +7258,25 @@
         <v>54</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="F43" s="6" t="s">
         <v>38</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="J43" s="6" t="s">
         <v>39</v>
@@ -7250,19 +7293,19 @@
         <v>54</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>41</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>33</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="J44" s="6" t="s">
         <v>34</v>
@@ -7279,19 +7322,19 @@
         <v>54</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>37</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="F45" s="6" t="s">
         <v>33</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="J45" s="6" t="s">
         <v>34</v>
@@ -7308,19 +7351,19 @@
         <v>54</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>33</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="J46" s="6" t="s">
         <v>34</v>
@@ -7349,13 +7392,13 @@
         <v>38</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="J47" s="6" t="s">
         <v>39</v>
@@ -7372,25 +7415,25 @@
         <v>50</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>38</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="J48" s="6" t="s">
         <v>49</v>
@@ -7419,7 +7462,7 @@
         <v>33</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="J49" s="6" t="s">
         <v>34</v>
@@ -7436,25 +7479,25 @@
         <v>221</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>38</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="J50" s="6" t="s">
         <v>49</v>
@@ -7471,25 +7514,25 @@
         <v>50</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="F51" s="6" t="s">
         <v>38</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="J51" s="6" t="s">
         <v>49</v>
@@ -7506,25 +7549,25 @@
         <v>52</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>57</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="J52" s="6" t="s">
         <v>49</v>
@@ -7541,25 +7584,25 @@
         <v>221</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>225</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="F53" s="6" t="s">
         <v>38</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="J53" s="6" t="s">
         <v>49</v>
@@ -7576,19 +7619,19 @@
         <v>52</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>33</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="J54" s="6" t="s">
         <v>34</v>
@@ -7605,19 +7648,19 @@
         <v>46</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>41</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>33</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="J55" s="6" t="s">
         <v>34</v>
@@ -7634,19 +7677,19 @@
         <v>52</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>33</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="J56" s="6" t="s">
         <v>34</v>
@@ -7660,28 +7703,28 @@
         <v>56</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="F57" s="6" t="s">
         <v>38</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="J57" s="6" t="s">
         <v>39</v>
@@ -8085,7 +8128,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{257D8841-47DB-4538-8583-7B1B1FF5827D}">
-  <dimension ref="A1:L1011"/>
+  <dimension ref="A1:L1009"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" style="13" customWidth="1"/>
@@ -8099,7 +8142,8 @@
     <col min="9" max="9" width="8.7109375" style="28" customWidth="1"/>
     <col min="10" max="10" width="12.85546875" style="26" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="49" style="13" customWidth="1"/>
-    <col min="12" max="14" width="5.7109375" style="13" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" style="14" customWidth="1"/>
+    <col min="13" max="14" width="5.7109375" style="13" customWidth="1"/>
     <col min="15" max="27" width="8.7109375" style="13" customWidth="1"/>
     <col min="28" max="16384" width="14.42578125" style="13"/>
   </cols>
@@ -8110,14 +8154,14 @@
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="29" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="D1" s="25"/>
       <c r="E1" s="22"/>
     </row>
     <row r="2" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="19"/>
@@ -8133,7 +8177,7 @@
     </row>
     <row r="4" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="19"/>
@@ -8145,7 +8189,7 @@
         <v>212</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>213</v>
@@ -8174,31 +8218,31 @@
       <c r="K5" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="L5" s="12" t="s">
-        <v>571</v>
+      <c r="L5" s="25" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="H6" s="27">
         <v>46141</v>
@@ -8210,33 +8254,33 @@
         <v>46141</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>616</v>
-      </c>
-      <c r="L6" s="15" t="s">
-        <v>617</v>
+        <v>609</v>
+      </c>
+      <c r="L6" s="24" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="21" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="G7" s="26" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="H7" s="27">
         <v>46141</v>
@@ -8248,33 +8292,33 @@
         <v>46141</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>618</v>
-      </c>
-      <c r="L7" s="15">
+        <v>611</v>
+      </c>
+      <c r="L7" s="24">
         <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="G8" s="26" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="H8" s="27">
         <v>46141</v>
@@ -8286,33 +8330,33 @@
         <v>46141</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>619</v>
-      </c>
-      <c r="L8" s="15" t="s">
-        <v>620</v>
+        <v>612</v>
+      </c>
+      <c r="L8" s="24" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="G9" s="26" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="H9" s="27">
         <v>46141</v>
@@ -8324,33 +8368,33 @@
         <v>46141</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>621</v>
-      </c>
-      <c r="L9" s="15" t="s">
-        <v>622</v>
+        <v>614</v>
+      </c>
+      <c r="L9" s="24" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="G10" s="26" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="H10" s="27">
         <v>46141</v>
@@ -8362,33 +8406,33 @@
         <v>46141</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>623</v>
-      </c>
-      <c r="L10" s="15" t="s">
-        <v>624</v>
+        <v>616</v>
+      </c>
+      <c r="L10" s="24" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="G11" s="26" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="H11" s="27">
         <v>46141</v>
@@ -8400,33 +8444,33 @@
         <v>46141</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>625</v>
-      </c>
-      <c r="L11" s="15" t="s">
-        <v>626</v>
+        <v>618</v>
+      </c>
+      <c r="L11" s="24" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="H12" s="27">
         <v>46141</v>
@@ -8438,33 +8482,33 @@
         <v>46141</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>627</v>
-      </c>
-      <c r="L12" s="15" t="s">
-        <v>628</v>
+        <v>620</v>
+      </c>
+      <c r="L12" s="24" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="G13" s="26" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="H13" s="27">
         <v>46141</v>
@@ -8476,33 +8520,33 @@
         <v>46141</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>629</v>
-      </c>
-      <c r="L13" s="15" t="s">
-        <v>630</v>
+        <v>622</v>
+      </c>
+      <c r="L13" s="24" t="s">
+        <v>623</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="G14" s="26" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="H14" s="27">
         <v>46141</v>
@@ -8514,33 +8558,33 @@
         <v>46141</v>
       </c>
       <c r="K14" s="15" t="s">
-        <v>631</v>
-      </c>
-      <c r="L14" s="15" t="s">
-        <v>632</v>
+        <v>624</v>
+      </c>
+      <c r="L14" s="24" t="s">
+        <v>625</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="G15" s="26" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="H15" s="27">
         <v>46141</v>
@@ -8552,33 +8596,33 @@
         <v>46141</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>633</v>
-      </c>
-      <c r="L15" s="15">
+        <v>626</v>
+      </c>
+      <c r="L15" s="24">
         <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="G16" s="26" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="H16" s="27">
         <v>46141</v>
@@ -8590,33 +8634,33 @@
         <v>46141</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>634</v>
-      </c>
-      <c r="L16" s="15" t="s">
-        <v>635</v>
+        <v>627</v>
+      </c>
+      <c r="L16" s="24" t="s">
+        <v>628</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="G17" s="26" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="H17" s="27">
         <v>46141</v>
@@ -8628,30 +8672,30 @@
         <v>46141</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>636</v>
-      </c>
-      <c r="L17" s="15">
+        <v>629</v>
+      </c>
+      <c r="L17" s="24">
         <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="G18" s="26" t="s">
         <v>283</v>
@@ -8666,30 +8710,30 @@
         <v>46141</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>637</v>
-      </c>
-      <c r="L18" s="15" t="s">
-        <v>638</v>
+        <v>630</v>
+      </c>
+      <c r="L18" s="24" t="s">
+        <v>631</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="G19" s="26" t="s">
         <v>283</v>
@@ -8704,30 +8748,30 @@
         <v>46141</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>639</v>
-      </c>
-      <c r="L19" s="15" t="s">
-        <v>628</v>
+        <v>632</v>
+      </c>
+      <c r="L19" s="24" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="D20" s="14" t="s">
         <v>37</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="G20" s="26" t="s">
         <v>283</v>
@@ -8742,30 +8786,30 @@
         <v>46141</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>640</v>
-      </c>
-      <c r="L20" s="15">
+        <v>633</v>
+      </c>
+      <c r="L20" s="24">
         <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="G21" s="26" t="s">
         <v>283</v>
@@ -8780,30 +8824,30 @@
         <v>46141</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>641</v>
-      </c>
-      <c r="L21" s="15">
+        <v>634</v>
+      </c>
+      <c r="L21" s="24">
         <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="G22" s="26" t="s">
         <v>283</v>
@@ -8818,21 +8862,21 @@
         <v>46141</v>
       </c>
       <c r="K22" s="15" t="s">
-        <v>642</v>
-      </c>
-      <c r="L22" s="15" t="s">
-        <v>643</v>
+        <v>635</v>
+      </c>
+      <c r="L22" s="24" t="s">
+        <v>636</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H23" s="27"/>
       <c r="J23" s="27"/>
       <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
+      <c r="L23" s="24"/>
     </row>
     <row r="24" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B24" s="17"/>
       <c r="C24" s="12"/>
@@ -8841,14 +8885,14 @@
       <c r="H24" s="27"/>
       <c r="J24" s="27"/>
       <c r="K24" s="15"/>
-      <c r="L24" s="15"/>
+      <c r="L24" s="24"/>
     </row>
     <row r="25" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
         <v>212</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>213</v>
@@ -8877,284 +8921,284 @@
       <c r="K25" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="L25" s="12" t="s">
-        <v>571</v>
+      <c r="L25" s="25" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="21" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="G26" s="26" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="H26" s="27">
         <v>46141</v>
       </c>
       <c r="I26" s="28" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="J26" s="27">
         <v>46138</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>645</v>
-      </c>
-      <c r="L26" s="15">
+        <v>638</v>
+      </c>
+      <c r="L26" s="24">
         <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="21" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="G27" s="26" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="H27" s="27">
         <v>46141</v>
       </c>
       <c r="I27" s="28" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="J27" s="27">
         <v>46138</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>646</v>
-      </c>
-      <c r="L27" s="15">
+        <v>639</v>
+      </c>
+      <c r="L27" s="24">
         <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="21" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="G28" s="26" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="H28" s="27">
         <v>46141</v>
       </c>
       <c r="I28" s="28" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="J28" s="27">
         <v>46138</v>
       </c>
       <c r="K28" s="15" t="s">
-        <v>647</v>
-      </c>
-      <c r="L28" s="15">
+        <v>640</v>
+      </c>
+      <c r="L28" s="24">
         <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="21" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="G29" s="26" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="H29" s="27">
         <v>46141</v>
       </c>
       <c r="I29" s="28" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="J29" s="27">
         <v>46138</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>648</v>
-      </c>
-      <c r="L29" s="15">
+        <v>641</v>
+      </c>
+      <c r="L29" s="24">
         <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="21" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="G30" s="26" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="H30" s="27">
         <v>46141</v>
       </c>
       <c r="J30" s="27"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
+      <c r="K30" s="28"/>
+      <c r="L30" s="24"/>
     </row>
     <row r="31" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="21" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="G31" s="26" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="H31" s="27">
         <v>46141</v>
       </c>
       <c r="J31" s="27"/>
-      <c r="K31" s="15"/>
-      <c r="L31" s="15"/>
+      <c r="K31" s="28"/>
+      <c r="L31" s="24"/>
     </row>
     <row r="32" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="21" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="G32" s="26" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="H32" s="27">
         <v>46141</v>
       </c>
       <c r="J32" s="27"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="15"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="24"/>
     </row>
     <row r="33" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="21" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="G33" s="26" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="H33" s="27">
         <v>46141</v>
       </c>
       <c r="J33" s="27"/>
-      <c r="K33" s="15"/>
-      <c r="L33" s="15"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="24"/>
     </row>
     <row r="34" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C34" s="15" t="s">
         <v>285</v>
@@ -9166,7 +9210,7 @@
         <v>286</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="G34" s="26" t="s">
         <v>283</v>
@@ -9175,15 +9219,15 @@
         <v>46140</v>
       </c>
       <c r="J34" s="27"/>
-      <c r="K34" s="15"/>
-      <c r="L34" s="15"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="24"/>
     </row>
     <row r="35" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C35" s="15" t="s">
         <v>287</v>
@@ -9195,7 +9239,7 @@
         <v>288</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="G35" s="26" t="s">
         <v>283</v>
@@ -9204,15 +9248,15 @@
         <v>46140</v>
       </c>
       <c r="J35" s="27"/>
-      <c r="K35" s="15"/>
-      <c r="L35" s="15"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="24"/>
     </row>
     <row r="36" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C36" s="15" t="s">
         <v>289</v>
@@ -9224,7 +9268,7 @@
         <v>291</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="G36" s="26" t="s">
         <v>283</v>
@@ -9233,15 +9277,15 @@
         <v>46140</v>
       </c>
       <c r="J36" s="27"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="15"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="24"/>
     </row>
     <row r="37" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>292</v>
@@ -9253,7 +9297,7 @@
         <v>294</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="G37" s="26" t="s">
         <v>283</v>
@@ -9262,15 +9306,15 @@
         <v>46140</v>
       </c>
       <c r="J37" s="27"/>
-      <c r="K37" s="15"/>
-      <c r="L37" s="15"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="24"/>
     </row>
     <row r="38" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C38" s="15" t="s">
         <v>304</v>
@@ -9282,33 +9326,33 @@
         <v>306</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>568</v>
-      </c>
-      <c r="G38" s="26" t="s">
-        <v>283</v>
+        <v>560</v>
+      </c>
+      <c r="G38" s="28" t="s">
+        <v>637</v>
       </c>
       <c r="H38" s="27">
-        <v>46140</v>
+        <v>46138</v>
       </c>
       <c r="I38" s="28" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="J38" s="27">
         <v>46138</v>
       </c>
       <c r="K38" s="15" t="s">
-        <v>650</v>
-      </c>
-      <c r="L38" s="15">
+        <v>643</v>
+      </c>
+      <c r="L38" s="24">
         <v>42</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="16" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C39" s="15" t="s">
         <v>269</v>
@@ -9320,7 +9364,7 @@
         <v>332</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="G39" s="26" t="s">
         <v>283</v>
@@ -9329,15 +9373,15 @@
         <v>46140</v>
       </c>
       <c r="J39" s="27"/>
-      <c r="K39" s="15"/>
-      <c r="L39" s="15"/>
+      <c r="K39" s="28"/>
+      <c r="L39" s="24"/>
     </row>
     <row r="40" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C40" s="15" t="s">
         <v>271</v>
@@ -9349,7 +9393,7 @@
         <v>332</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="G40" s="26" t="s">
         <v>283</v>
@@ -9358,15 +9402,15 @@
         <v>46140</v>
       </c>
       <c r="J40" s="27"/>
-      <c r="K40" s="15"/>
-      <c r="L40" s="15"/>
+      <c r="K40" s="28"/>
+      <c r="L40" s="24"/>
     </row>
     <row r="41" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="16" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="C41" s="15" t="s">
         <v>264</v>
@@ -9378,7 +9422,7 @@
         <v>317</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="G41" s="26" t="s">
         <v>283</v>
@@ -9387,15 +9431,15 @@
         <v>46140</v>
       </c>
       <c r="J41" s="27"/>
-      <c r="K41" s="15"/>
-      <c r="L41" s="15"/>
+      <c r="K41" s="28"/>
+      <c r="L41" s="24"/>
     </row>
     <row r="42" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="16" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>265</v>
@@ -9407,7 +9451,7 @@
         <v>319</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="G42" s="26" t="s">
         <v>283</v>
@@ -9416,15 +9460,15 @@
         <v>46140</v>
       </c>
       <c r="J42" s="27"/>
-      <c r="K42" s="15"/>
-      <c r="L42" s="15"/>
+      <c r="K42" s="28"/>
+      <c r="L42" s="24"/>
     </row>
     <row r="43" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="16" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>266</v>
@@ -9436,7 +9480,7 @@
         <v>321</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="G43" s="26" t="s">
         <v>283</v>
@@ -9445,15 +9489,15 @@
         <v>46140</v>
       </c>
       <c r="J43" s="27"/>
-      <c r="K43" s="15"/>
-      <c r="L43" s="15"/>
+      <c r="K43" s="28"/>
+      <c r="L43" s="24"/>
     </row>
     <row r="44" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>267</v>
@@ -9465,7 +9509,7 @@
         <v>323</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="G44" s="26" t="s">
         <v>283</v>
@@ -9474,15 +9518,15 @@
         <v>46140</v>
       </c>
       <c r="J44" s="27"/>
-      <c r="K44" s="15"/>
-      <c r="L44" s="15"/>
+      <c r="K44" s="28"/>
+      <c r="L44" s="24"/>
     </row>
     <row r="45" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="16" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="C45" s="15" t="s">
         <v>268</v>
@@ -9494,7 +9538,7 @@
         <v>325</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="G45" s="26" t="s">
         <v>283</v>
@@ -9503,27 +9547,27 @@
         <v>46140</v>
       </c>
       <c r="J45" s="27"/>
-      <c r="K45" s="15"/>
-      <c r="L45" s="15"/>
+      <c r="K45" s="28"/>
+      <c r="L45" s="24"/>
     </row>
     <row r="46" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="16" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="D46" s="24" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="G46" s="26" t="s">
         <v>283</v>
@@ -9532,18 +9576,18 @@
         <v>46142</v>
       </c>
       <c r="J46" s="27"/>
-      <c r="K46" s="15"/>
-      <c r="L46" s="15"/>
+      <c r="K46" s="28"/>
+      <c r="L46" s="24"/>
     </row>
     <row r="47" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H47" s="27"/>
       <c r="J47" s="27"/>
       <c r="K47" s="15"/>
-      <c r="L47" s="15"/>
+      <c r="L47" s="24"/>
     </row>
     <row r="48" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="17" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B48" s="17"/>
       <c r="C48" s="12"/>
@@ -9552,14 +9596,14 @@
       <c r="H48" s="27"/>
       <c r="J48" s="27"/>
       <c r="K48" s="15"/>
-      <c r="L48" s="15"/>
+      <c r="L48" s="24"/>
     </row>
     <row r="49" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
         <v>212</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="C49" s="12" t="s">
         <v>213</v>
@@ -9588,327 +9632,345 @@
       <c r="K49" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="L49" s="12" t="s">
-        <v>571</v>
+      <c r="L49" s="25" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="21" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="G50" s="26" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="H50" s="27">
         <v>46141</v>
       </c>
       <c r="J50" s="27"/>
-      <c r="K50" s="15"/>
-      <c r="L50" s="15"/>
+      <c r="K50" s="28"/>
+      <c r="L50" s="24"/>
     </row>
     <row r="51" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="21" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="G51" s="26" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="H51" s="27">
         <v>46141</v>
       </c>
       <c r="J51" s="27"/>
-      <c r="K51" s="15"/>
-      <c r="L51" s="15"/>
+      <c r="K51" s="28"/>
+      <c r="L51" s="24"/>
     </row>
     <row r="52" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="21" t="s">
-        <v>497</v>
-      </c>
-      <c r="B52" s="21" t="s">
-        <v>449</v>
+      <c r="A52" s="13" t="s">
+        <v>480</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>441</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>345</v>
+        <v>415</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>344</v>
+        <v>414</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>343</v>
+        <v>413</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="G52" s="26" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="H52" s="27">
         <v>46141</v>
       </c>
-      <c r="J52" s="27"/>
-      <c r="K52" s="15"/>
-      <c r="L52" s="15"/>
+      <c r="I52" s="28" t="s">
+        <v>637</v>
+      </c>
+      <c r="J52" s="27">
+        <v>46138</v>
+      </c>
+      <c r="K52" s="15" t="s">
+        <v>642</v>
+      </c>
+      <c r="L52" s="24">
+        <v>42</v>
+      </c>
     </row>
     <row r="53" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="G53" s="26" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="H53" s="27">
         <v>46141</v>
       </c>
       <c r="I53" s="28" t="s">
-        <v>644</v>
+        <v>283</v>
       </c>
       <c r="J53" s="27">
-        <v>46138</v>
-      </c>
-      <c r="K53" s="15" t="s">
-        <v>649</v>
-      </c>
-      <c r="L53" s="15">
-        <v>42</v>
+        <v>46143</v>
+      </c>
+      <c r="K53" s="28" t="s">
+        <v>721</v>
+      </c>
+      <c r="L53" s="24" t="s">
+        <v>711</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="G54" s="26" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="H54" s="27">
         <v>46141</v>
       </c>
-      <c r="J54" s="27"/>
-      <c r="K54" s="15"/>
-      <c r="L54" s="15"/>
+      <c r="I54" s="28" t="s">
+        <v>283</v>
+      </c>
+      <c r="J54" s="27">
+        <v>46143</v>
+      </c>
+      <c r="K54" s="28" t="s">
+        <v>722</v>
+      </c>
+      <c r="L54" s="24" t="s">
+        <v>712</v>
+      </c>
     </row>
     <row r="55" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>415</v>
+        <v>362</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>414</v>
+        <v>381</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>413</v>
+        <v>380</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="G55" s="26" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="H55" s="27">
         <v>46141</v>
       </c>
       <c r="J55" s="27"/>
-      <c r="K55" s="15"/>
-      <c r="L55" s="15"/>
+      <c r="K55" s="28"/>
+      <c r="L55" s="24"/>
     </row>
     <row r="56" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="13" t="s">
+        <v>501</v>
+      </c>
+      <c r="B56" s="13" t="s">
+        <v>442</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="D56" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="E56" s="15" t="s">
+        <v>377</v>
+      </c>
+      <c r="F56" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="G56" s="26" t="s">
         <v>507</v>
-      </c>
-      <c r="B56" s="13" t="s">
-        <v>448</v>
-      </c>
-      <c r="C56" s="13" t="s">
-        <v>368</v>
-      </c>
-      <c r="D56" s="14" t="s">
-        <v>387</v>
-      </c>
-      <c r="E56" s="15" t="s">
-        <v>386</v>
-      </c>
-      <c r="F56" s="13" t="s">
-        <v>569</v>
-      </c>
-      <c r="G56" s="26" t="s">
-        <v>515</v>
       </c>
       <c r="H56" s="27">
         <v>46141</v>
       </c>
       <c r="J56" s="27"/>
-      <c r="K56" s="15"/>
-      <c r="L56" s="15"/>
+      <c r="K56" s="28"/>
+      <c r="L56" s="24"/>
     </row>
     <row r="57" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="13" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="G57" s="26" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="H57" s="27">
         <v>46141</v>
       </c>
       <c r="J57" s="27"/>
-      <c r="K57" s="15"/>
-      <c r="L57" s="15"/>
+      <c r="K57" s="28"/>
+      <c r="L57" s="24"/>
     </row>
     <row r="58" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="13" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>382</v>
+        <v>272</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="E58" s="15" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="G58" s="26" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="H58" s="27">
         <v>46141</v>
       </c>
       <c r="J58" s="27"/>
-      <c r="K58" s="15"/>
-      <c r="L58" s="15"/>
+      <c r="K58" s="28"/>
+      <c r="L58" s="24"/>
     </row>
     <row r="59" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="13" t="s">
-        <v>510</v>
+      <c r="A59" s="16" t="s">
+        <v>527</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>448</v>
-      </c>
-      <c r="C59" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="D59" s="14" t="s">
-        <v>379</v>
+        <v>441</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="D59" s="24" t="s">
+        <v>296</v>
       </c>
       <c r="E59" s="15" t="s">
-        <v>378</v>
+        <v>297</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="G59" s="26" t="s">
-        <v>515</v>
+        <v>283</v>
       </c>
       <c r="H59" s="27">
-        <v>46141</v>
+        <v>46140</v>
       </c>
       <c r="J59" s="27"/>
-      <c r="K59" s="15"/>
-      <c r="L59" s="15"/>
+      <c r="K59" s="28"/>
+      <c r="L59" s="24"/>
     </row>
     <row r="60" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="16" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D60" s="24" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="G60" s="26" t="s">
         <v>283</v>
@@ -9917,27 +9979,27 @@
         <v>46140</v>
       </c>
       <c r="J60" s="27"/>
-      <c r="K60" s="15"/>
-      <c r="L60" s="15"/>
+      <c r="K60" s="28"/>
+      <c r="L60" s="24"/>
     </row>
     <row r="61" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="16" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D61" s="24" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E61" s="15" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="G61" s="26" t="s">
         <v>283</v>
@@ -9945,28 +10007,37 @@
       <c r="H61" s="27">
         <v>46140</v>
       </c>
-      <c r="J61" s="27"/>
-      <c r="K61" s="15"/>
-      <c r="L61" s="15"/>
+      <c r="I61" s="28" t="s">
+        <v>283</v>
+      </c>
+      <c r="J61" s="27">
+        <v>46143</v>
+      </c>
+      <c r="K61" s="28" t="s">
+        <v>723</v>
+      </c>
+      <c r="L61" s="24" t="s">
+        <v>713</v>
+      </c>
     </row>
     <row r="62" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="16" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="D62" s="24" t="s">
-        <v>302</v>
+        <v>327</v>
       </c>
       <c r="E62" s="15" t="s">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="G62" s="26" t="s">
         <v>283</v>
@@ -9975,27 +10046,27 @@
         <v>46140</v>
       </c>
       <c r="J62" s="27"/>
-      <c r="K62" s="15"/>
-      <c r="L62" s="15"/>
+      <c r="K62" s="28"/>
+      <c r="L62" s="24"/>
     </row>
     <row r="63" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="16" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D63" s="24" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E63" s="15" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="G63" s="26" t="s">
         <v>283</v>
@@ -10004,254 +10075,263 @@
         <v>46140</v>
       </c>
       <c r="J63" s="27"/>
-      <c r="K63" s="15"/>
-      <c r="L63" s="15"/>
+      <c r="K63" s="28"/>
+      <c r="L63" s="24"/>
     </row>
     <row r="64" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="16" t="s">
-        <v>539</v>
-      </c>
-      <c r="B64" s="13" t="s">
-        <v>449</v>
-      </c>
-      <c r="C64" s="15" t="s">
-        <v>329</v>
-      </c>
-      <c r="D64" s="24" t="s">
-        <v>330</v>
-      </c>
-      <c r="E64" s="15" t="s">
-        <v>331</v>
-      </c>
-      <c r="F64" s="13" t="s">
-        <v>569</v>
-      </c>
-      <c r="G64" s="26" t="s">
-        <v>283</v>
-      </c>
-      <c r="H64" s="27">
-        <v>46140</v>
-      </c>
-      <c r="J64" s="27"/>
       <c r="K64" s="15"/>
-      <c r="L64" s="15"/>
+      <c r="L64" s="24"/>
     </row>
     <row r="65" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="B65" s="17"/>
+      <c r="C65" s="12"/>
+      <c r="D65" s="25"/>
+      <c r="E65" s="22"/>
       <c r="K65" s="15"/>
-      <c r="L65" s="15"/>
+      <c r="L65" s="24"/>
     </row>
     <row r="66" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="17" t="s">
-        <v>342</v>
-      </c>
-      <c r="B66" s="17"/>
-      <c r="C66" s="12"/>
-      <c r="D66" s="25"/>
-      <c r="E66" s="22"/>
-      <c r="K66" s="15"/>
-      <c r="L66" s="15"/>
+      <c r="A66" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="B66" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="E66" s="22" t="s">
+        <v>215</v>
+      </c>
+      <c r="F66" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="G66" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="H66" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="I66" s="22" t="s">
+        <v>284</v>
+      </c>
+      <c r="J66" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="K66" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="L66" s="25" t="s">
+        <v>563</v>
+      </c>
     </row>
     <row r="67" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="B67" s="12" t="s">
+      <c r="A67" s="21" t="s">
+        <v>491</v>
+      </c>
+      <c r="B67" s="21" t="s">
         <v>443</v>
       </c>
-      <c r="C67" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="D67" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="E67" s="22" t="s">
-        <v>215</v>
-      </c>
-      <c r="F67" s="12" t="s">
-        <v>336</v>
-      </c>
-      <c r="G67" s="12" t="s">
-        <v>334</v>
-      </c>
-      <c r="H67" s="12" t="s">
-        <v>335</v>
-      </c>
-      <c r="I67" s="22" t="s">
-        <v>284</v>
-      </c>
-      <c r="J67" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="K67" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="L67" s="12" t="s">
-        <v>571</v>
-      </c>
+      <c r="C67" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="D67" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="E67" s="15" t="s">
+        <v>338</v>
+      </c>
+      <c r="F67" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="G67" s="26" t="s">
+        <v>509</v>
+      </c>
+      <c r="H67" s="27">
+        <v>46141</v>
+      </c>
+      <c r="J67" s="27"/>
+      <c r="K67" s="28"/>
+      <c r="L67" s="24"/>
     </row>
     <row r="68" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="21" t="s">
-        <v>498</v>
-      </c>
-      <c r="B68" s="21" t="s">
-        <v>449</v>
+      <c r="A68" s="13" t="s">
+        <v>483</v>
+      </c>
+      <c r="B68" s="13" t="s">
+        <v>441</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>341</v>
+        <v>406</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>340</v>
+        <v>405</v>
       </c>
       <c r="E68" s="15" t="s">
-        <v>339</v>
+        <v>404</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="G68" s="26" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="H68" s="27">
         <v>46141</v>
       </c>
-      <c r="J68" s="27"/>
-      <c r="K68" s="15"/>
-      <c r="L68" s="15"/>
+      <c r="I68" s="28" t="s">
+        <v>283</v>
+      </c>
+      <c r="J68" s="27">
+        <v>46143</v>
+      </c>
+      <c r="K68" s="28" t="s">
+        <v>724</v>
+      </c>
+      <c r="L68" s="24" t="s">
+        <v>714</v>
+      </c>
     </row>
     <row r="69" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="13" t="s">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>412</v>
+        <v>371</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>411</v>
+        <v>368</v>
       </c>
       <c r="E69" s="15" t="s">
-        <v>410</v>
+        <v>370</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="G69" s="26" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="H69" s="27">
         <v>46141</v>
       </c>
       <c r="J69" s="27"/>
-      <c r="K69" s="15"/>
-      <c r="L69" s="15"/>
+      <c r="K69" s="28"/>
+      <c r="L69" s="24"/>
     </row>
     <row r="70" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="13" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="G70" s="26" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="H70" s="27">
         <v>46141</v>
       </c>
       <c r="J70" s="27"/>
-      <c r="K70" s="15"/>
-      <c r="L70" s="15"/>
+      <c r="K70" s="28"/>
+      <c r="L70" s="24"/>
     </row>
     <row r="71" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="13" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="F71" s="13" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="G71" s="26" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="H71" s="27">
         <v>46141</v>
       </c>
       <c r="J71" s="27"/>
-      <c r="K71" s="15"/>
-      <c r="L71" s="15"/>
+      <c r="K71" s="28"/>
+      <c r="L71" s="24"/>
     </row>
     <row r="72" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="13" t="s">
-        <v>513</v>
+      <c r="A72" s="16" t="s">
+        <v>532</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>448</v>
-      </c>
-      <c r="C72" s="13" t="s">
-        <v>371</v>
-      </c>
-      <c r="D72" s="14" t="s">
-        <v>370</v>
+        <v>463</v>
+      </c>
+      <c r="C72" s="15" t="s">
+        <v>464</v>
+      </c>
+      <c r="D72" s="24" t="s">
+        <v>465</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>369</v>
+        <v>466</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="G72" s="26" t="s">
-        <v>515</v>
+        <v>283</v>
       </c>
       <c r="H72" s="27">
-        <v>46141</v>
+        <v>46140</v>
       </c>
       <c r="J72" s="27"/>
-      <c r="K72" s="15"/>
-      <c r="L72" s="15"/>
+      <c r="K72" s="28"/>
+      <c r="L72" s="24"/>
     </row>
     <row r="73" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="16" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="B73" s="13" t="s">
+        <v>467</v>
+      </c>
+      <c r="C73" s="15" t="s">
+        <v>468</v>
+      </c>
+      <c r="D73" s="24" t="s">
+        <v>333</v>
+      </c>
+      <c r="E73" s="15" t="s">
         <v>469</v>
       </c>
-      <c r="C73" s="15" t="s">
-        <v>470</v>
-      </c>
-      <c r="D73" s="24" t="s">
-        <v>471</v>
-      </c>
-      <c r="E73" s="15" t="s">
-        <v>472</v>
-      </c>
       <c r="F73" s="13" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="G73" s="26" t="s">
         <v>283</v>
@@ -10260,27 +10340,27 @@
         <v>46140</v>
       </c>
       <c r="J73" s="27"/>
-      <c r="K73" s="15"/>
-      <c r="L73" s="15"/>
+      <c r="K73" s="28"/>
+      <c r="L73" s="24"/>
     </row>
     <row r="74" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="16" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>474</v>
+        <v>444</v>
       </c>
       <c r="D74" s="24" t="s">
-        <v>333</v>
+        <v>277</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="F74" s="13" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="G74" s="26" t="s">
         <v>283</v>
@@ -10289,27 +10369,27 @@
         <v>46140</v>
       </c>
       <c r="J74" s="27"/>
-      <c r="K74" s="15"/>
-      <c r="L74" s="15"/>
+      <c r="K74" s="28"/>
+      <c r="L74" s="24"/>
     </row>
     <row r="75" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="16" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>473</v>
+        <v>445</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="D75" s="24" t="s">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="E75" s="15" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="F75" s="13" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="G75" s="26" t="s">
         <v>283</v>
@@ -10318,166 +10398,193 @@
         <v>46140</v>
       </c>
       <c r="J75" s="27"/>
-      <c r="K75" s="15"/>
-      <c r="L75" s="15"/>
+      <c r="K75" s="28"/>
+      <c r="L75" s="24"/>
     </row>
     <row r="76" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="16" t="s">
-        <v>543</v>
-      </c>
-      <c r="B76" s="13" t="s">
-        <v>451</v>
-      </c>
-      <c r="C76" s="15" t="s">
-        <v>452</v>
-      </c>
-      <c r="D76" s="24" t="s">
-        <v>296</v>
-      </c>
-      <c r="E76" s="15" t="s">
-        <v>477</v>
-      </c>
-      <c r="F76" s="13" t="s">
-        <v>569</v>
-      </c>
-      <c r="G76" s="26" t="s">
-        <v>283</v>
-      </c>
-      <c r="H76" s="27">
-        <v>46140</v>
-      </c>
+      <c r="H76" s="27"/>
       <c r="J76" s="27"/>
       <c r="K76" s="15"/>
-      <c r="L76" s="15"/>
+      <c r="L76" s="24"/>
     </row>
     <row r="77" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H77" s="27"/>
-      <c r="J77" s="27"/>
+      <c r="A77" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="B77" s="17"/>
       <c r="K77" s="15"/>
-      <c r="L77" s="15"/>
+      <c r="L77" s="24"/>
     </row>
     <row r="78" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="17" t="s">
-        <v>338</v>
-      </c>
-      <c r="B78" s="17"/>
-      <c r="K78" s="15"/>
-      <c r="L78" s="15"/>
+      <c r="A78" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="B78" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="E78" s="22" t="s">
+        <v>215</v>
+      </c>
+      <c r="F78" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="G78" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="H78" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="I78" s="22" t="s">
+        <v>284</v>
+      </c>
+      <c r="J78" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="K78" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="L78" s="25" t="s">
+        <v>563</v>
+      </c>
     </row>
     <row r="79" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="B79" s="12" t="s">
-        <v>443</v>
-      </c>
-      <c r="C79" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="D79" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="E79" s="22" t="s">
-        <v>215</v>
-      </c>
-      <c r="F79" s="12" t="s">
-        <v>336</v>
-      </c>
-      <c r="G79" s="12" t="s">
-        <v>334</v>
-      </c>
-      <c r="H79" s="12" t="s">
-        <v>335</v>
-      </c>
-      <c r="I79" s="22" t="s">
-        <v>284</v>
-      </c>
-      <c r="J79" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="K79" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="L79" s="12" t="s">
-        <v>571</v>
+      <c r="A79" s="13" t="s">
+        <v>484</v>
+      </c>
+      <c r="B79" s="13" t="s">
+        <v>441</v>
+      </c>
+      <c r="C79" s="13" t="s">
+        <v>403</v>
+      </c>
+      <c r="D79" s="14" t="s">
+        <v>402</v>
+      </c>
+      <c r="E79" s="15" t="s">
+        <v>401</v>
+      </c>
+      <c r="F79" s="13" t="s">
+        <v>560</v>
+      </c>
+      <c r="G79" s="26" t="s">
+        <v>508</v>
+      </c>
+      <c r="H79" s="27">
+        <v>46141</v>
+      </c>
+      <c r="I79" s="28" t="s">
+        <v>283</v>
+      </c>
+      <c r="J79" s="27">
+        <v>46143</v>
+      </c>
+      <c r="K79" s="28" t="s">
+        <v>725</v>
+      </c>
+      <c r="L79" s="24">
+        <v>48</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="13" t="s">
-        <v>490</v>
+      <c r="A80" s="16" t="s">
+        <v>536</v>
       </c>
       <c r="B80" s="13" t="s">
         <v>447</v>
       </c>
-      <c r="C80" s="13" t="s">
-        <v>409</v>
-      </c>
-      <c r="D80" s="14" t="s">
-        <v>408</v>
+      <c r="C80" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="D80" s="24" t="s">
+        <v>310</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>407</v>
+        <v>274</v>
       </c>
       <c r="F80" s="13" t="s">
-        <v>568</v>
-      </c>
-      <c r="G80" s="26" t="s">
-        <v>516</v>
+        <v>560</v>
+      </c>
+      <c r="G80" s="28" t="s">
+        <v>637</v>
       </c>
       <c r="H80" s="27">
-        <v>46141</v>
-      </c>
-      <c r="J80" s="27"/>
-      <c r="K80" s="15"/>
-      <c r="L80" s="15"/>
+        <v>46138</v>
+      </c>
+      <c r="I80" s="28" t="s">
+        <v>637</v>
+      </c>
+      <c r="J80" s="27">
+        <v>46138</v>
+      </c>
+      <c r="K80" s="15" t="s">
+        <v>644</v>
+      </c>
+      <c r="L80" s="24">
+        <v>42</v>
+      </c>
     </row>
     <row r="81" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="13" t="s">
-        <v>514</v>
+      <c r="A81" s="16" t="s">
+        <v>537</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>448</v>
-      </c>
-      <c r="C81" s="13" t="s">
-        <v>367</v>
-      </c>
-      <c r="D81" s="14" t="s">
-        <v>366</v>
+        <v>447</v>
+      </c>
+      <c r="C81" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="D81" s="24" t="s">
+        <v>311</v>
       </c>
       <c r="E81" s="15" t="s">
-        <v>365</v>
+        <v>312</v>
       </c>
       <c r="F81" s="13" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="G81" s="26" t="s">
-        <v>515</v>
+        <v>283</v>
       </c>
       <c r="H81" s="27">
-        <v>46141</v>
-      </c>
-      <c r="J81" s="27"/>
-      <c r="K81" s="15"/>
-      <c r="L81" s="15"/>
+        <v>46140</v>
+      </c>
+      <c r="I81" s="28" t="s">
+        <v>283</v>
+      </c>
+      <c r="J81" s="27">
+        <v>46143</v>
+      </c>
+      <c r="K81" s="28" t="s">
+        <v>726</v>
+      </c>
+      <c r="L81" s="24" t="s">
+        <v>715</v>
+      </c>
     </row>
     <row r="82" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="16" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D82" s="24" t="s">
-        <v>310</v>
+        <v>277</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>274</v>
+        <v>308</v>
       </c>
       <c r="F82" s="13" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="G82" s="26" t="s">
         <v>283</v>
@@ -10486,36 +10593,36 @@
         <v>46140</v>
       </c>
       <c r="I82" s="28" t="s">
-        <v>644</v>
+        <v>283</v>
       </c>
       <c r="J82" s="27">
-        <v>46138</v>
-      </c>
-      <c r="K82" s="15" t="s">
-        <v>651</v>
-      </c>
-      <c r="L82" s="15">
-        <v>42</v>
+        <v>46143</v>
+      </c>
+      <c r="K82" s="28" t="s">
+        <v>727</v>
+      </c>
+      <c r="L82" s="24" t="s">
+        <v>716</v>
       </c>
     </row>
     <row r="83" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="16" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>275</v>
+        <v>313</v>
       </c>
       <c r="D83" s="24" t="s">
-        <v>311</v>
+        <v>278</v>
       </c>
       <c r="E83" s="15" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F83" s="13" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="G83" s="26" t="s">
         <v>283</v>
@@ -10523,334 +10630,314 @@
       <c r="H83" s="27">
         <v>46140</v>
       </c>
-      <c r="J83" s="27"/>
-      <c r="K83" s="15"/>
-      <c r="L83" s="15"/>
+      <c r="I83" s="28" t="s">
+        <v>283</v>
+      </c>
+      <c r="J83" s="27">
+        <v>46143</v>
+      </c>
+      <c r="K83" s="28" t="s">
+        <v>728</v>
+      </c>
+      <c r="L83" s="24" t="s">
+        <v>717</v>
+      </c>
     </row>
     <row r="84" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="16" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>276</v>
-      </c>
-      <c r="D84" s="24" t="s">
-        <v>277</v>
+        <v>279</v>
+      </c>
+      <c r="D84" s="24">
+        <v>9</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F84" s="13" t="s">
-        <v>568</v>
-      </c>
-      <c r="G84" s="26" t="s">
-        <v>283</v>
+        <v>560</v>
+      </c>
+      <c r="G84" s="28" t="s">
+        <v>637</v>
       </c>
       <c r="H84" s="27">
-        <v>46140</v>
-      </c>
-      <c r="J84" s="27"/>
-      <c r="K84" s="15"/>
-      <c r="L84" s="15"/>
+        <v>46138</v>
+      </c>
+      <c r="I84" s="28" t="s">
+        <v>637</v>
+      </c>
+      <c r="J84" s="27">
+        <v>46138</v>
+      </c>
+      <c r="K84" s="15" t="s">
+        <v>645</v>
+      </c>
+      <c r="L84" s="24">
+        <v>42</v>
+      </c>
     </row>
     <row r="85" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="16" t="s">
-        <v>547</v>
+      <c r="A85" s="13" t="s">
+        <v>558</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>453</v>
-      </c>
-      <c r="C85" s="15" t="s">
-        <v>313</v>
-      </c>
-      <c r="D85" s="24" t="s">
-        <v>278</v>
-      </c>
-      <c r="E85" s="15" t="s">
-        <v>314</v>
+        <v>447</v>
+      </c>
+      <c r="C85" s="13" t="s">
+        <v>548</v>
+      </c>
+      <c r="D85" s="14" t="s">
+        <v>549</v>
+      </c>
+      <c r="E85" s="13" t="s">
+        <v>550</v>
       </c>
       <c r="F85" s="13" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="G85" s="26" t="s">
         <v>283</v>
       </c>
       <c r="H85" s="27">
-        <v>46140</v>
-      </c>
-      <c r="J85" s="27"/>
-      <c r="K85" s="15"/>
-      <c r="L85" s="15"/>
+        <v>46142</v>
+      </c>
+      <c r="I85" s="28" t="s">
+        <v>283</v>
+      </c>
+      <c r="J85" s="27">
+        <v>46143</v>
+      </c>
+      <c r="K85" s="28" t="s">
+        <v>729</v>
+      </c>
+      <c r="L85" s="24" t="s">
+        <v>718</v>
+      </c>
     </row>
     <row r="86" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="16" t="s">
-        <v>548</v>
+      <c r="A86" s="13" t="s">
+        <v>559</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>453</v>
-      </c>
-      <c r="C86" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="D86" s="24">
-        <v>9</v>
-      </c>
-      <c r="E86" s="15" t="s">
-        <v>315</v>
+        <v>447</v>
+      </c>
+      <c r="C86" s="13" t="s">
+        <v>554</v>
+      </c>
+      <c r="D86" s="14" t="s">
+        <v>555</v>
+      </c>
+      <c r="E86" s="13" t="s">
+        <v>556</v>
       </c>
       <c r="F86" s="13" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="G86" s="26" t="s">
         <v>283</v>
       </c>
       <c r="H86" s="27">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="I86" s="28" t="s">
-        <v>644</v>
+        <v>283</v>
       </c>
       <c r="J86" s="27">
+        <v>46143</v>
+      </c>
+      <c r="K86" s="28" t="s">
+        <v>730</v>
+      </c>
+      <c r="L86" s="24" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="16" t="s">
+        <v>541</v>
+      </c>
+      <c r="B87" s="13" t="s">
+        <v>447</v>
+      </c>
+      <c r="C87" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="D87" s="24" t="s">
+        <v>280</v>
+      </c>
+      <c r="E87" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="F87" s="13" t="s">
+        <v>560</v>
+      </c>
+      <c r="G87" s="28" t="s">
+        <v>637</v>
+      </c>
+      <c r="H87" s="27">
         <v>46138</v>
       </c>
-      <c r="K86" s="15" t="s">
-        <v>652</v>
-      </c>
-      <c r="L86" s="15">
+      <c r="I87" s="28" t="s">
+        <v>637</v>
+      </c>
+      <c r="J87" s="27">
+        <v>46138</v>
+      </c>
+      <c r="K87" s="15" t="s">
+        <v>646</v>
+      </c>
+      <c r="L87" s="24" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="B88" s="13" t="s">
+        <v>447</v>
+      </c>
+      <c r="C88" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="D88" s="24" t="s">
+        <v>280</v>
+      </c>
+      <c r="E88" s="15" t="s">
+        <v>308</v>
+      </c>
+      <c r="F88" s="13" t="s">
+        <v>560</v>
+      </c>
+      <c r="G88" s="28" t="s">
+        <v>637</v>
+      </c>
+      <c r="H88" s="27">
+        <v>46138</v>
+      </c>
+      <c r="I88" s="28" t="s">
+        <v>637</v>
+      </c>
+      <c r="J88" s="27">
+        <v>46138</v>
+      </c>
+      <c r="K88" s="15" t="s">
+        <v>648</v>
+      </c>
+      <c r="L88" s="24">
         <v>42</v>
       </c>
-    </row>
-    <row r="87" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="13" t="s">
-        <v>566</v>
-      </c>
-      <c r="B87" s="13" t="s">
-        <v>453</v>
-      </c>
-      <c r="C87" s="13" t="s">
-        <v>556</v>
-      </c>
-      <c r="D87" s="14" t="s">
-        <v>557</v>
-      </c>
-      <c r="E87" s="13" t="s">
-        <v>558</v>
-      </c>
-      <c r="F87" s="13" t="s">
-        <v>568</v>
-      </c>
-      <c r="G87" s="26" t="s">
-        <v>283</v>
-      </c>
-      <c r="H87" s="27">
-        <v>46142</v>
-      </c>
-      <c r="J87" s="27"/>
-      <c r="K87" s="15"/>
-      <c r="L87" s="15"/>
-    </row>
-    <row r="88" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="13" t="s">
-        <v>567</v>
-      </c>
-      <c r="B88" s="13" t="s">
-        <v>453</v>
-      </c>
-      <c r="C88" s="13" t="s">
-        <v>562</v>
-      </c>
-      <c r="D88" s="14" t="s">
-        <v>563</v>
-      </c>
-      <c r="E88" s="13" t="s">
-        <v>564</v>
-      </c>
-      <c r="F88" s="13" t="s">
-        <v>568</v>
-      </c>
-      <c r="G88" s="26" t="s">
-        <v>283</v>
-      </c>
-      <c r="H88" s="27">
-        <v>46142</v>
-      </c>
-      <c r="J88" s="27"/>
-      <c r="K88" s="15"/>
-      <c r="L88" s="15"/>
     </row>
     <row r="89" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="16" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="B89" s="13" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D89" s="24" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E89" s="15" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F89" s="13" t="s">
-        <v>568</v>
-      </c>
-      <c r="G89" s="26" t="s">
-        <v>283</v>
+        <v>560</v>
+      </c>
+      <c r="G89" s="28" t="s">
+        <v>637</v>
       </c>
       <c r="H89" s="27">
-        <v>46140</v>
+        <v>46138</v>
       </c>
       <c r="I89" s="28" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="J89" s="27">
         <v>46138</v>
       </c>
       <c r="K89" s="15" t="s">
-        <v>653</v>
-      </c>
-      <c r="L89" s="15" t="s">
-        <v>654</v>
+        <v>649</v>
+      </c>
+      <c r="L89" s="24">
+        <v>42</v>
       </c>
     </row>
     <row r="90" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="16" t="s">
-        <v>550</v>
+      <c r="A90" s="13" t="s">
+        <v>557</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>453</v>
-      </c>
-      <c r="C90" s="15" t="s">
-        <v>271</v>
-      </c>
-      <c r="D90" s="24" t="s">
-        <v>280</v>
-      </c>
-      <c r="E90" s="15" t="s">
-        <v>308</v>
+        <v>447</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>551</v>
+      </c>
+      <c r="D90" s="14" t="s">
+        <v>552</v>
+      </c>
+      <c r="E90" s="13" t="s">
+        <v>553</v>
       </c>
       <c r="F90" s="13" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="G90" s="26" t="s">
         <v>283</v>
       </c>
       <c r="H90" s="27">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="I90" s="28" t="s">
-        <v>644</v>
+        <v>283</v>
       </c>
       <c r="J90" s="27">
-        <v>46138</v>
-      </c>
-      <c r="K90" s="15" t="s">
-        <v>655</v>
-      </c>
-      <c r="L90" s="15">
-        <v>42</v>
+        <v>46143</v>
+      </c>
+      <c r="K90" s="28" t="s">
+        <v>731</v>
+      </c>
+      <c r="L90" s="24" t="s">
+        <v>720</v>
       </c>
     </row>
     <row r="91" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="16" t="s">
-        <v>551</v>
-      </c>
-      <c r="B91" s="13" t="s">
-        <v>453</v>
-      </c>
-      <c r="C91" s="15" t="s">
-        <v>281</v>
-      </c>
-      <c r="D91" s="24" t="s">
-        <v>282</v>
-      </c>
-      <c r="E91" s="15" t="s">
-        <v>309</v>
-      </c>
-      <c r="F91" s="13" t="s">
-        <v>568</v>
-      </c>
-      <c r="G91" s="26" t="s">
-        <v>283</v>
-      </c>
-      <c r="H91" s="27">
-        <v>46140</v>
-      </c>
-      <c r="I91" s="28" t="s">
-        <v>644</v>
-      </c>
-      <c r="J91" s="27">
-        <v>46138</v>
-      </c>
-      <c r="K91" s="15" t="s">
-        <v>656</v>
-      </c>
-      <c r="L91" s="15">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="13" t="s">
-        <v>565</v>
-      </c>
-      <c r="B92" s="13" t="s">
-        <v>453</v>
-      </c>
-      <c r="C92" s="13" t="s">
-        <v>559</v>
-      </c>
-      <c r="D92" s="14" t="s">
-        <v>560</v>
-      </c>
-      <c r="E92" s="13" t="s">
-        <v>561</v>
-      </c>
-      <c r="F92" s="13" t="s">
-        <v>568</v>
-      </c>
-      <c r="G92" s="26" t="s">
-        <v>283</v>
-      </c>
-      <c r="H92" s="27">
-        <v>46142</v>
-      </c>
-      <c r="J92" s="27"/>
-      <c r="K92" s="15"/>
-      <c r="L92" s="15"/>
-    </row>
-    <row r="93" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93"/>
-      <c r="H93" s="27"/>
-      <c r="J93" s="27"/>
-    </row>
-    <row r="97" spans="8:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H97" s="27"/>
-      <c r="J97" s="27"/>
-    </row>
-    <row r="98" spans="8:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H98" s="27"/>
-      <c r="J98" s="27"/>
-    </row>
-    <row r="99" spans="8:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="8:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="8:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="8:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="8:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="8:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="8:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="8:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="8:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="8:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="8:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="8:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="8:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="8:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="A91"/>
+      <c r="H91" s="27"/>
+      <c r="J91" s="27"/>
+    </row>
+    <row r="95" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H95" s="27"/>
+      <c r="J95" s="27"/>
+    </row>
+    <row r="96" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H96" s="27"/>
+      <c r="J96" s="27"/>
+    </row>
+    <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="113" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="114" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="115" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -11748,10 +11835,478 @@
     <row r="1007" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1008" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1009" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1010" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1011" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6C9405E-667B-4C37-897B-C4E67350D257}">
+  <dimension ref="A1:L12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="10" max="10" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="186" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F1" t="s">
+        <v>336</v>
+      </c>
+      <c r="G1" t="s">
+        <v>334</v>
+      </c>
+      <c r="H1" t="s">
+        <v>335</v>
+      </c>
+      <c r="I1" t="s">
+        <v>608</v>
+      </c>
+      <c r="J1" t="s">
+        <v>217</v>
+      </c>
+      <c r="K1" t="s">
+        <v>218</v>
+      </c>
+      <c r="L1" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>481</v>
+      </c>
+      <c r="B2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C2" t="s">
+        <v>412</v>
+      </c>
+      <c r="D2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E2" t="s">
+        <v>410</v>
+      </c>
+      <c r="F2" t="s">
+        <v>560</v>
+      </c>
+      <c r="G2" t="s">
+        <v>508</v>
+      </c>
+      <c r="H2" s="9">
+        <v>46141</v>
+      </c>
+      <c r="I2" t="s">
+        <v>283</v>
+      </c>
+      <c r="J2" s="9">
+        <v>46143</v>
+      </c>
+      <c r="K2" t="s">
+        <v>721</v>
+      </c>
+      <c r="L2" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>482</v>
+      </c>
+      <c r="B3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C3" t="s">
+        <v>409</v>
+      </c>
+      <c r="D3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E3" t="s">
+        <v>407</v>
+      </c>
+      <c r="F3" t="s">
+        <v>560</v>
+      </c>
+      <c r="G3" t="s">
+        <v>508</v>
+      </c>
+      <c r="H3" s="9">
+        <v>46141</v>
+      </c>
+      <c r="I3" t="s">
+        <v>283</v>
+      </c>
+      <c r="J3" s="9">
+        <v>46143</v>
+      </c>
+      <c r="K3" t="s">
+        <v>722</v>
+      </c>
+      <c r="L3" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>529</v>
+      </c>
+      <c r="B4" t="s">
+        <v>441</v>
+      </c>
+      <c r="C4" t="s">
+        <v>301</v>
+      </c>
+      <c r="D4" t="s">
+        <v>302</v>
+      </c>
+      <c r="E4" t="s">
+        <v>303</v>
+      </c>
+      <c r="F4" t="s">
+        <v>560</v>
+      </c>
+      <c r="G4" t="s">
+        <v>283</v>
+      </c>
+      <c r="H4" s="9">
+        <v>46140</v>
+      </c>
+      <c r="I4" t="s">
+        <v>283</v>
+      </c>
+      <c r="J4" s="9">
+        <v>46143</v>
+      </c>
+      <c r="K4" t="s">
+        <v>723</v>
+      </c>
+      <c r="L4" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>483</v>
+      </c>
+      <c r="B5" t="s">
+        <v>441</v>
+      </c>
+      <c r="C5" t="s">
+        <v>406</v>
+      </c>
+      <c r="D5" t="s">
+        <v>405</v>
+      </c>
+      <c r="E5" t="s">
+        <v>404</v>
+      </c>
+      <c r="F5" t="s">
+        <v>560</v>
+      </c>
+      <c r="G5" t="s">
+        <v>508</v>
+      </c>
+      <c r="H5" s="9">
+        <v>46141</v>
+      </c>
+      <c r="I5" t="s">
+        <v>283</v>
+      </c>
+      <c r="J5" s="9">
+        <v>46143</v>
+      </c>
+      <c r="K5" t="s">
+        <v>724</v>
+      </c>
+      <c r="L5" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>484</v>
+      </c>
+      <c r="B6" t="s">
+        <v>441</v>
+      </c>
+      <c r="C6" t="s">
+        <v>403</v>
+      </c>
+      <c r="D6" t="s">
+        <v>402</v>
+      </c>
+      <c r="E6" t="s">
+        <v>401</v>
+      </c>
+      <c r="F6" t="s">
+        <v>560</v>
+      </c>
+      <c r="G6" t="s">
+        <v>508</v>
+      </c>
+      <c r="H6" s="9">
+        <v>46141</v>
+      </c>
+      <c r="I6" t="s">
+        <v>283</v>
+      </c>
+      <c r="J6" s="9">
+        <v>46143</v>
+      </c>
+      <c r="K6" t="s">
+        <v>725</v>
+      </c>
+      <c r="L6">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>537</v>
+      </c>
+      <c r="B7" t="s">
+        <v>447</v>
+      </c>
+      <c r="C7" t="s">
+        <v>275</v>
+      </c>
+      <c r="D7" t="s">
+        <v>311</v>
+      </c>
+      <c r="E7" t="s">
+        <v>312</v>
+      </c>
+      <c r="F7" t="s">
+        <v>560</v>
+      </c>
+      <c r="G7" t="s">
+        <v>283</v>
+      </c>
+      <c r="H7" s="9">
+        <v>46140</v>
+      </c>
+      <c r="I7" t="s">
+        <v>283</v>
+      </c>
+      <c r="J7" s="9">
+        <v>46143</v>
+      </c>
+      <c r="K7" t="s">
+        <v>726</v>
+      </c>
+      <c r="L7" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>538</v>
+      </c>
+      <c r="B8" t="s">
+        <v>447</v>
+      </c>
+      <c r="C8" t="s">
+        <v>276</v>
+      </c>
+      <c r="D8" t="s">
+        <v>277</v>
+      </c>
+      <c r="E8" t="s">
+        <v>308</v>
+      </c>
+      <c r="F8" t="s">
+        <v>560</v>
+      </c>
+      <c r="G8" t="s">
+        <v>283</v>
+      </c>
+      <c r="H8" s="9">
+        <v>46140</v>
+      </c>
+      <c r="I8" t="s">
+        <v>283</v>
+      </c>
+      <c r="J8" s="9">
+        <v>46143</v>
+      </c>
+      <c r="K8" t="s">
+        <v>727</v>
+      </c>
+      <c r="L8" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>539</v>
+      </c>
+      <c r="B9" t="s">
+        <v>447</v>
+      </c>
+      <c r="C9" t="s">
+        <v>313</v>
+      </c>
+      <c r="D9" t="s">
+        <v>278</v>
+      </c>
+      <c r="E9" t="s">
+        <v>314</v>
+      </c>
+      <c r="F9" t="s">
+        <v>560</v>
+      </c>
+      <c r="G9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H9" s="9">
+        <v>46140</v>
+      </c>
+      <c r="I9" t="s">
+        <v>283</v>
+      </c>
+      <c r="J9" s="9">
+        <v>46143</v>
+      </c>
+      <c r="K9" t="s">
+        <v>728</v>
+      </c>
+      <c r="L9" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>558</v>
+      </c>
+      <c r="B10" t="s">
+        <v>447</v>
+      </c>
+      <c r="C10" t="s">
+        <v>548</v>
+      </c>
+      <c r="D10" t="s">
+        <v>549</v>
+      </c>
+      <c r="E10" t="s">
+        <v>550</v>
+      </c>
+      <c r="F10" t="s">
+        <v>560</v>
+      </c>
+      <c r="G10" t="s">
+        <v>283</v>
+      </c>
+      <c r="H10" s="9">
+        <v>46142</v>
+      </c>
+      <c r="I10" t="s">
+        <v>283</v>
+      </c>
+      <c r="J10" s="9">
+        <v>46143</v>
+      </c>
+      <c r="K10" t="s">
+        <v>729</v>
+      </c>
+      <c r="L10" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>559</v>
+      </c>
+      <c r="B11" t="s">
+        <v>447</v>
+      </c>
+      <c r="C11" t="s">
+        <v>554</v>
+      </c>
+      <c r="D11" t="s">
+        <v>555</v>
+      </c>
+      <c r="E11" t="s">
+        <v>556</v>
+      </c>
+      <c r="F11" t="s">
+        <v>560</v>
+      </c>
+      <c r="G11" t="s">
+        <v>283</v>
+      </c>
+      <c r="H11" s="9">
+        <v>46142</v>
+      </c>
+      <c r="I11" t="s">
+        <v>283</v>
+      </c>
+      <c r="J11" s="9">
+        <v>46143</v>
+      </c>
+      <c r="K11" t="s">
+        <v>730</v>
+      </c>
+      <c r="L11" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>557</v>
+      </c>
+      <c r="B12" t="s">
+        <v>447</v>
+      </c>
+      <c r="C12" t="s">
+        <v>551</v>
+      </c>
+      <c r="D12" t="s">
+        <v>552</v>
+      </c>
+      <c r="E12" t="s">
+        <v>553</v>
+      </c>
+      <c r="F12" t="s">
+        <v>560</v>
+      </c>
+      <c r="G12" t="s">
+        <v>283</v>
+      </c>
+      <c r="H12" s="9">
+        <v>46142</v>
+      </c>
+      <c r="I12" t="s">
+        <v>283</v>
+      </c>
+      <c r="J12" s="9">
+        <v>46143</v>
+      </c>
+      <c r="K12" t="s">
+        <v>731</v>
+      </c>
+      <c r="L12" t="s">
+        <v>720</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/tests/Verificacoes.xlsx
+++ b/tests/Verificacoes.xlsx
@@ -15178,112 +15178,116 @@
       </c>
     </row>
     <row r="18" ht="90" customHeight="1">
-      <c r="A18" s="35" t="n">
+      <c r="A18" s="37" t="n">
         <v>45</v>
       </c>
-      <c r="B18" s="35" t="inlineStr">
-        <is>
-          <t>Testes</t>
-        </is>
-      </c>
-      <c r="C18" s="35" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
+        <is>
+          <t>MVC</t>
+        </is>
+      </c>
+      <c r="C18" s="37" t="inlineStr">
         <is>
           <t>Cobertura de observação do Controller quanto a coordenação, dependências e fecho controlado</t>
         </is>
       </c>
-      <c r="D18" s="35" t="inlineStr">
+      <c r="D18" s="37" t="inlineStr">
         <is>
           <t>Controller.cs</t>
         </is>
       </c>
-      <c r="E18" s="35" t="inlineStr">
+      <c r="E18" s="37" t="inlineStr">
         <is>
           <t>O Controller deve coordenar View e Model, sem lógica de negócio, e encerrar sem Environment.Exit</t>
         </is>
       </c>
-      <c r="F18" s="35" t="inlineStr">
-        <is>
-          <t>Conforme</t>
-        </is>
-      </c>
-      <c r="G18" s="35" t="inlineStr">
-        <is>
-          <t>Controller instancia View e Model, medeia fluxos, obtém resultado via IResultadoOperacao (T5) e decide apresentação; sem lógica de negócio; encerra com _executando = false; subscrições de eventos do Model removidas do construtor (código comentado)</t>
-        </is>
-      </c>
-      <c r="H18" s="35" t="inlineStr">
-        <is>
-          <t>Eventos do Model não subscritos — ver ID#11</t>
-        </is>
-      </c>
-      <c r="I18" s="35" t="n"/>
-      <c r="J18" s="35" t="inlineStr">
-        <is>
-          <t>Baixa</t>
-        </is>
-      </c>
-      <c r="K18" s="36" t="n">
+      <c r="F18" s="37" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="G18" s="37" t="inlineStr">
+        <is>
+          <t>Controller instancia View e Model, medeia fluxos e decide apresentação com base em IResultadoOperacao devolvido pelo Model (T5); sem lógica de negócio; encerra com _executando = false. Os resultados das operações chegam à View por retorno de IResultadoOperacao e não por eventos — os eventos OperacaoConcluida e ErroStockInsuficiente foram removidos das subscrições do Controller sem decisão formal registada sobre a mudança de mecanismo (ver ID#11).</t>
+        </is>
+      </c>
+      <c r="H18" s="37" t="inlineStr">
+        <is>
+          <t>A substituição do mecanismo de notificação por eventos pelo retorno de IResultadoOperacao não foi uma decisão explícita da equipa — resultou da refactorização T5 sem registo formal. Os eventos continuam declarados no Model como código morto.</t>
+        </is>
+      </c>
+      <c r="I18" s="37" t="inlineStr">
+        <is>
+          <t>Tomar decisão formal: remover os eventos do Model ou voltar a subscrevê-los no Controller. Registar a decisão antes de fechar T5.7.</t>
+        </is>
+      </c>
+      <c r="J18" s="37" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K18" s="38" t="n">
         <v>46161</v>
       </c>
-      <c r="L18" s="43" t="inlineStr">
+      <c r="L18" s="37" t="inlineStr">
         <is>
           <t>Recheck</t>
         </is>
       </c>
     </row>
     <row r="19" ht="105" customHeight="1">
-      <c r="A19" s="37" t="n">
+      <c r="A19" s="33" t="n">
         <v>46</v>
       </c>
-      <c r="B19" s="37" t="inlineStr">
-        <is>
-          <t>Excepções</t>
-        </is>
-      </c>
-      <c r="C19" s="37" t="inlineStr">
+      <c r="B19" s="33" t="inlineStr">
+        <is>
+          <t>MVC</t>
+        </is>
+      </c>
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>Excepções implementadas respeitam o estilo MVC em todos os componentes</t>
         </is>
       </c>
-      <c r="D19" s="37" t="inlineStr">
+      <c r="D19" s="33" t="inlineStr">
         <is>
           <t>Controller.cs / Model.cs / View.cs</t>
         </is>
       </c>
-      <c r="E19" s="37" t="inlineStr">
+      <c r="E19" s="33" t="inlineStr">
         <is>
           <t>O tratamento de erros não deve ficar concentrado só num componente e deve respeitar as responsabilidades MVC</t>
         </is>
       </c>
-      <c r="F19" s="37" t="inlineStr">
-        <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="G19" s="37" t="inlineStr">
-        <is>
-          <t>Erros de input tratados no Controller; resultado de domínio via IResultadoOperacao (T5) — Controller verifica resultado.Sucesso e delega apresentação à View; stock insuficiente ainda dispara ErroStockInsuficiente no Model mas o evento não está subscrito; falhas de persistência propagadas ao Controller via excepção</t>
-        </is>
-      </c>
-      <c r="H19" s="37" t="inlineStr">
-        <is>
-          <t>Evento ErroStockInsuficiente disparado mas não subscrito (código morto); falta registo formal de cenários de falha técnica de JSON (ID#49)</t>
-        </is>
-      </c>
-      <c r="I19" s="37" t="inlineStr">
-        <is>
-          <t>Resolver ID#11 (eventos mortos); executar e registar cenários de falha de persistência JSON</t>
-        </is>
-      </c>
-      <c r="J19" s="37" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
-      <c r="K19" s="38" t="n">
+      <c r="F19" s="33" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="G19" s="33" t="inlineStr">
+        <is>
+          <t>Erros de input tratados no Controller; resultado de domínio via IResultadoOperacao — Controller verifica resultado.Sucesso e delega apresentação à View. Os eventos ErroStockInsuficiente e OperacaoConcluida estão declarados no Model mas não estão subscritos no Controller após refactorização T5 — os resultados chegam à View por retorno directo de IResultadoOperacao, não por eventos. Esta mudança de mecanismo não tem decisão formal registada.</t>
+        </is>
+      </c>
+      <c r="H19" s="33" t="inlineStr">
+        <is>
+          <t>A arquitectura definida previa que as notificações do Model chegassem à View por eventos; na versão actual chegam por retorno de IResultadoOperacao. Os eventos declarados no Model são código morto. A categoria desta verificação foi corrigida de Excepções para MVC — trata-se de uma questão arquitectónica, não de tratamento de erros.</t>
+        </is>
+      </c>
+      <c r="I19" s="33" t="inlineStr">
+        <is>
+          <t>Decidir formalmente o mecanismo de notificação adoptado para T5.7 e alinhar código e documentação em conformidade (ver ID#11 e ID#45).</t>
+        </is>
+      </c>
+      <c r="J19" s="33" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K19" s="34" t="n">
         <v>46161</v>
       </c>
-      <c r="L19" s="44" t="inlineStr">
+      <c r="L19" s="33" t="inlineStr">
         <is>
           <t>Recheck</t>
         </is>
@@ -15586,17 +15590,17 @@
       </c>
       <c r="G25" s="35" t="inlineStr">
         <is>
-          <t>Validação formal do verificador (Laurentino Reis, 19 Mai 2026) — main pós-merge: (1) Compilação: dotnet build succeeded, net9.0, zero erros (ID#61); (2) Execução: todos os fluxos funcionais, persistência confirmada (ID#62); (3) MVC mantido: Controller medeia View e Model, View sem using do Model (IDs #5, #60); (4) Interfaces em uso real: IProduto e IResultadoOperacao em Contracts, Produto implementa IProduto, View recebe IEnumerable&lt;IProduto&gt; em MostrarStock e MostrarListaReposicao (IDs #57, #58, #59); (5) List&lt;Produto&gt; substituído por IEnumerable&lt;IProduto&gt; nos contratos públicos da View; Controller usa List&lt;IProduto&gt; como buffer local — aceitável; ref List&lt;IProduto&gt; no Model pendente (ID#56/#59); (6) IGestorStock/IStockModel não implementada — registada como melhoria futura (ID#65); (7) PRs #17, #18, #19 merged, main limpa e sincronizada (ID#64); (8) Json.NET como API oficial confirmado (ID#66); (9) Sem push directo para main (ID#67). Bloqueios antes de fechar T5.7: ID#56/#59 (ref dispensável) e ID#11 (eventos não subscritos).</t>
+          <t>Validação formal do verificador (Laurentino Reis, 19 Mai 2026) — main pós-merge: (1) Compilação: dotnet build succeeded, net9.0, zero erros (ID#61); (2) Execução: todos os fluxos funcionais, persistência confirmada (ID#62); (3) MVC mantido: Controller medeia View e Model, View sem using do Model (IDs#5, #60); (4) Interfaces em uso real: IProduto e IResultadoOperacao em Contracts, Produto implementa IProduto, View recebe IEnumerable&lt;IProduto&gt; (IDs#57, #58, #59); (5) List&lt;Produto&gt; substituído nos contratos públicos da View; ref List&lt;IProduto&gt; no Model pendente (ID#56/#59); (6) IGestorStock/IStockModel não implementada — registada como melhoria futura (ID#65); (7) PRs #17, #18, #19 merged, main limpa (ID#64); (8) Json.NET como API oficial confirmado (ID#66); (9) Sem push directo para main (ID#67).</t>
         </is>
       </c>
       <c r="H25" s="35" t="inlineStr">
         <is>
-          <t>Bloqueios identificados: ID#56/#59 (ref List&lt;IProduto&gt; dispensável no Model) e ID#11 (eventos OperacaoConcluida/ErroStockInsuficiente declarados mas não subscritos — código morto)</t>
+          <t>Dois bloqueios com natureza distinta identificados: (A) ID#56/#59 — ref List&lt;IProduto&gt; dispensável no Model, questão de limpeza de código; (B) ID#11/#45/#46 — os resultados do Model chegam à View por retorno de IResultadoOperacao e não por eventos, contrariando a arquitectura definida; os eventos declarados no Model são código morto; esta é uma decisão arquitectónica por tomar formalmente, não apenas limpeza de código.</t>
         </is>
       </c>
       <c r="I25" s="35" t="inlineStr">
         <is>
-          <t>Resolver ID#56/#59 substituindo ref por retorno de IEnumerable&lt;IProduto&gt;; decidir sobre eventos do Model (remover ou voltar a subscrever)</t>
+          <t>Resolver ID#56/#59 (ref → IEnumerable); tomar decisão formal sobre o mecanismo de notificação do Model (eventos vs IResultadoOperacao) e registar antes de fechar T5.7 (IDs#11, #45, #46).</t>
         </is>
       </c>
       <c r="J25" s="35" t="inlineStr">
@@ -15607,7 +15611,7 @@
       <c r="K25" s="36" t="n">
         <v>46161</v>
       </c>
-      <c r="L25" s="43" t="inlineStr">
+      <c r="L25" s="35" t="inlineStr">
         <is>
           <t>Novo</t>
         </is>
